--- a/Ticket Image/超市小票识别_2026-03-23.xlsx
+++ b/Ticket Image/超市小票识别_2026-03-23.xlsx
@@ -464,6 +464,12 @@
       <c r="C3" t="str">
         <v>鸡腿</v>
       </c>
+      <c r="D3">
+        <v>7.8</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
       <c r="F3">
         <v>7.8</v>
       </c>
@@ -480,6 +486,12 @@
       </c>
       <c r="C4" t="str">
         <v>西兰花</v>
+      </c>
+      <c r="D4">
+        <v>3.4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4">
         <v>3.4</v>

--- a/Ticket Image/超市小票识别_2026-03-23.xlsx
+++ b/Ticket Image/超市小票识别_2026-03-23.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -509,22 +509,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>购物时间</v>
+        <v>2026-03-23 10:04:51</v>
       </c>
       <c r="B6" t="str">
-        <v>超市名称</v>
+        <v>大利家精品超市谢村店</v>
       </c>
       <c r="C6" t="str">
-        <v>商品名称</v>
-      </c>
-      <c r="D6" t="str">
-        <v>数量</v>
-      </c>
-      <c r="E6" t="str">
-        <v>单价</v>
-      </c>
-      <c r="F6" t="str">
-        <v>小计</v>
+        <v>鸡腿</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>7.8</v>
+      </c>
+      <c r="F6">
+        <v>7.8</v>
       </c>
     </row>
     <row r="7">
@@ -535,16 +535,16 @@
         <v>大利家精品超市谢村店</v>
       </c>
       <c r="C7" t="str">
-        <v>鸡腿</v>
+        <v>蔬菜鹿茸菇</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="F7">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
@@ -555,16 +555,16 @@
         <v>大利家精品超市谢村店</v>
       </c>
       <c r="C8" t="str">
-        <v>蔬菜鹿茸菇</v>
+        <v>珍珠苦瓜</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="F8">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -575,61 +575,21 @@
         <v>大利家精品超市谢村店</v>
       </c>
       <c r="C9" t="str">
-        <v>珍珠苦瓜</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>3.1</v>
+        <v>合计</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
       </c>
       <c r="F9">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2026-03-23 10:04:51</v>
-      </c>
-      <c r="B10" t="str">
-        <v>大利家精品超市谢村店</v>
-      </c>
-      <c r="C10" t="str">
-        <v>合计</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10">
         <v>16.4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v/>
-      </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
   </ignoredErrors>
 </worksheet>
 </file>